--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-21.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-21.xlsx
@@ -763,16 +763,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="I2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="J2" t="n">
         <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -781,31 +781,31 @@
         <v>1.01</v>
       </c>
       <c r="N2" t="n">
-        <v>2.48</v>
+        <v>2.14</v>
       </c>
       <c r="O2" t="n">
         <v>1.21</v>
       </c>
       <c r="P2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
         <v>1.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S2" t="n">
         <v>2.36</v>
       </c>
       <c r="T2" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="V2" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="W2" t="n">
         <v>1.13</v>
@@ -865,52 +865,52 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2" t="n">
         <v>1.01</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>2.04</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
         <v>4.1</v>
@@ -966,7 +966,7 @@
         <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
         <v>1.38</v>
@@ -978,22 +978,22 @@
         <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R3" t="n">
         <v>1.39</v>
       </c>
       <c r="S3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
         <v>2.18</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>1.46</v>
       </c>
       <c r="G4" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H4" t="n">
         <v>7.4</v>
@@ -1163,7 +1163,7 @@
         <v>5.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.03</v>
@@ -1172,22 +1172,22 @@
         <v>5.5</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P4" t="n">
         <v>2.52</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R4" t="n">
         <v>1.62</v>
       </c>
       <c r="S4" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T4" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="U4" t="n">
         <v>2.14</v>
@@ -1196,7 +1196,7 @@
         <v>1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1217,7 +1217,7 @@
         <v>12.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
         <v>120</v>
@@ -1229,7 +1229,7 @@
         <v>10.5</v>
       </c>
       <c r="AH4" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI4" t="n">
         <v>1000</v>
@@ -1241,13 +1241,13 @@
         <v>15</v>
       </c>
       <c r="AL4" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
@@ -1256,13 +1256,13 @@
         <v>21</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>8.4</v>
+        <v>46</v>
       </c>
       <c r="AS4" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AT4" t="n">
         <v>9.6</v>
@@ -1271,10 +1271,10 @@
         <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
         <v>9</v>
@@ -1286,7 +1286,7 @@
         <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
         <v>11.5</v>
@@ -1295,20 +1295,20 @@
         <v>12.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF4" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BG4" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1339,19 +1339,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G5" t="n">
         <v>2.36</v>
       </c>
       <c r="H5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I5" t="n">
-        <v>3.55</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7</v>
+        <v>1.73</v>
       </c>
       <c r="K5" t="n">
         <v>3.9</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1536,10 +1536,10 @@
         <v>2.88</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="H6" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="I6" t="n">
         <v>2.76</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
         <v>1.96</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="I7" t="n">
         <v>2.18</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="Q7" t="n">
         <v>2.18</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -1933,7 +1933,7 @@
         <v>6.6</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K8" t="n">
         <v>1000</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
         <v>1.99</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H10" t="n">
         <v>1.9</v>
       </c>
       <c r="I10" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="G12" t="n">
         <v>4.3</v>
@@ -2706,10 +2706,10 @@
         <v>1.93</v>
       </c>
       <c r="I12" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
         <v>4.3</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.24</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
         <v>1.41</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -2891,16 +2891,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G13" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H13" t="n">
         <v>3.25</v>
       </c>
       <c r="I13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.8</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>1.8</v>
       </c>
       <c r="G14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
         <v>4.3</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3279,10 +3279,10 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G15" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H15" t="n">
         <v>3.65</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
         <v>3.35</v>
       </c>
       <c r="H17" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="I17" t="n">
         <v>2.32</v>
@@ -3691,16 +3691,16 @@
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
         <v>1.23</v>
       </c>
       <c r="P17" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R17" t="n">
         <v>1.53</v>
@@ -3721,13 +3721,13 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y17" t="n">
         <v>13</v>
       </c>
       <c r="Z17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA17" t="n">
         <v>32</v>
@@ -3748,7 +3748,7 @@
         <v>25</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH17" t="n">
         <v>15</v>
@@ -3784,13 +3784,13 @@
         <v>15</v>
       </c>
       <c r="AS17" t="n">
-        <v>19.5</v>
+        <v>27</v>
       </c>
       <c r="AT17" t="n">
         <v>15</v>
       </c>
       <c r="AU17" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV17" t="n">
         <v>10</v>
@@ -3799,7 +3799,7 @@
         <v>20</v>
       </c>
       <c r="AX17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY17" t="n">
         <v>13</v>
@@ -3808,7 +3808,7 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="BB17" t="n">
         <v>29</v>
@@ -3817,7 +3817,7 @@
         <v>21</v>
       </c>
       <c r="BD17" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="BE17" t="n">
         <v>50</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -3864,16 +3864,16 @@
         <v>1.74</v>
       </c>
       <c r="G18" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H18" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I18" t="n">
         <v>6</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K18" t="n">
         <v>4.4</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>3.4</v>
       </c>
       <c r="H20" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="I20" t="n">
         <v>3.2</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="H21" t="n">
-        <v>2.94</v>
+        <v>3.2</v>
       </c>
       <c r="I21" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>7.6</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="H23" t="n">
-        <v>1.28</v>
+        <v>1.74</v>
       </c>
       <c r="I23" t="n">
         <v>1.86</v>
@@ -4846,7 +4846,7 @@
         <v>4.2</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5225,7 +5225,7 @@
         <v>6.8</v>
       </c>
       <c r="H25" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="I25" t="n">
         <v>1.88</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5413,40 +5413,40 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="G26" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="H26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
         <v>1.63</v>
       </c>
-      <c r="I26" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.55</v>
-      </c>
       <c r="Q26" t="n">
-        <v>2.12</v>
+        <v>2.32</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5810,13 +5810,13 @@
         <v>3.7</v>
       </c>
       <c r="I28" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J28" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K28" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,7 +5831,7 @@
         <v>1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="Q28" t="n">
         <v>2.16</v>
@@ -5840,7 +5840,7 @@
         <v>1.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
         <v>1.91</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -5998,16 +5998,16 @@
         <v>1.92</v>
       </c>
       <c r="G29" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H29" t="n">
         <v>4.3</v>
       </c>
       <c r="I29" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J29" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K29" t="n">
         <v>3.75</v>
@@ -6025,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q29" t="n">
         <v>2.14</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6219,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6580,19 +6580,19 @@
         <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H32" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I32" t="n">
         <v>5.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K32" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6607,10 +6607,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
         <v>1.24</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7747,10 +7747,10 @@
         <v>2.28</v>
       </c>
       <c r="H38" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I38" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J38" t="n">
         <v>3.35</v>
@@ -7771,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -7977,7 +7977,7 @@
         <v>4.2</v>
       </c>
       <c r="T39" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U39" t="n">
         <v>2</v>
@@ -8022,7 +8022,7 @@
         <v>19.5</v>
       </c>
       <c r="AI39" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AJ39" t="n">
         <v>26</v>
@@ -8088,7 +8088,7 @@
         <v>26</v>
       </c>
       <c r="BE39" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF39" t="n">
         <v>17.5</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
         <v>1.19</v>
       </c>
       <c r="P43" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q43" t="n">
         <v>1.58</v>
@@ -8750,7 +8750,7 @@
         <v>1.65</v>
       </c>
       <c r="S43" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T43" t="n">
         <v>1.68</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
         <v>1.69</v>
       </c>
       <c r="U45" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
         <v>2.88</v>
       </c>
       <c r="I46" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J46" t="n">
         <v>3.65</v>
@@ -9329,7 +9329,7 @@
         <v>1.76</v>
       </c>
       <c r="R46" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S46" t="n">
         <v>2.92</v>
@@ -9338,7 +9338,7 @@
         <v>1.65</v>
       </c>
       <c r="U46" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -9356,7 +9356,7 @@
         <v>22</v>
       </c>
       <c r="AA46" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB46" t="n">
         <v>13</v>
@@ -9383,7 +9383,7 @@
         <v>38</v>
       </c>
       <c r="AJ46" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK46" t="n">
         <v>26</v>
@@ -9410,7 +9410,7 @@
         <v>18</v>
       </c>
       <c r="AS46" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AT46" t="n">
         <v>12</v>
@@ -9434,7 +9434,7 @@
         <v>14</v>
       </c>
       <c r="BA46" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="BB46" t="n">
         <v>22</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
         <v>1.96</v>
       </c>
       <c r="U47" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="V47" t="n">
         <v>0</v>
@@ -9571,7 +9571,7 @@
         <v>12.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI47" t="n">
         <v>1000</v>
@@ -9589,7 +9589,7 @@
         <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AO47" t="n">
         <v>1000</v>
@@ -9640,17 +9640,17 @@
         <v>21</v>
       </c>
       <c r="BE47" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BF47" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BG47" t="n">
         <v>16.5</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -9684,19 +9684,19 @@
         <v>2.66</v>
       </c>
       <c r="G48" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I48" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="J48" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="K48" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
         <v>6.6</v>
       </c>
       <c r="I49" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J49" t="n">
         <v>4.2</v>
@@ -9914,13 +9914,13 @@
         <v>1.41</v>
       </c>
       <c r="S49" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T49" t="n">
         <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V49" t="n">
         <v>0</v>
@@ -9950,7 +9950,7 @@
         <v>25</v>
       </c>
       <c r="AE49" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF49" t="n">
         <v>9</v>
@@ -9983,7 +9983,7 @@
         <v>160</v>
       </c>
       <c r="AP49" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AQ49" t="n">
         <v>19.5</v>
@@ -9995,7 +9995,7 @@
         <v>20</v>
       </c>
       <c r="AT49" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU49" t="n">
         <v>8.800000000000001</v>
@@ -10013,7 +10013,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ49" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA49" t="n">
         <v>38</v>
@@ -10022,7 +10022,7 @@
         <v>13.5</v>
       </c>
       <c r="BC49" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD49" t="n">
         <v>32</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10075,7 @@
         <v>2.18</v>
       </c>
       <c r="H50" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I50" t="n">
         <v>4.4</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -10263,16 +10263,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G51" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H51" t="n">
         <v>4.3</v>
       </c>
       <c r="I51" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J51" t="n">
         <v>3.55</v>
@@ -10293,10 +10293,10 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="Q51" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -10466,13 +10466,13 @@
         <v>2.96</v>
       </c>
       <c r="I52" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J52" t="n">
         <v>3</v>
       </c>
       <c r="K52" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -10487,10 +10487,10 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="G53" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="H53" t="n">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="I53" t="n">
         <v>6.4</v>
@@ -10666,7 +10666,7 @@
         <v>3.45</v>
       </c>
       <c r="K53" t="n">
-        <v>4.1</v>
+        <v>6.6</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="G55" t="n">
         <v>2.58</v>
@@ -11129,7 +11129,7 @@
         <v>120</v>
       </c>
       <c r="AJ55" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AK55" t="n">
         <v>40</v>
@@ -11147,7 +11147,7 @@
         <v>130</v>
       </c>
       <c r="AP55" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ55" t="n">
         <v>8</v>
@@ -11156,10 +11156,10 @@
         <v>19.5</v>
       </c>
       <c r="AS55" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT55" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU55" t="n">
         <v>6.6</v>
@@ -11180,7 +11180,7 @@
         <v>25</v>
       </c>
       <c r="BA55" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BB55" t="n">
         <v>23</v>
@@ -11192,17 +11192,17 @@
         <v>13.5</v>
       </c>
       <c r="BE55" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BF55" t="n">
         <v>25</v>
       </c>
       <c r="BG55" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -11233,7 +11233,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G56" t="n">
         <v>2.64</v>
@@ -11242,13 +11242,13 @@
         <v>3.2</v>
       </c>
       <c r="I56" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J56" t="n">
         <v>3.15</v>
       </c>
       <c r="K56" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -11263,10 +11263,10 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -11427,16 +11427,16 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G57" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="H57" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I57" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J57" t="n">
         <v>4</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -11633,7 +11633,7 @@
         <v>5.7</v>
       </c>
       <c r="J58" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="K58" t="n">
         <v>4.3</v>
@@ -11654,7 +11654,7 @@
         <v>2.02</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -12012,7 +12012,7 @@
         <v>2.48</v>
       </c>
       <c r="G60" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H60" t="n">
         <v>3.05</v>
@@ -12042,7 +12042,7 @@
         <v>1.75</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -12209,16 +12209,16 @@
         <v>2.9</v>
       </c>
       <c r="H61" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I61" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J61" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K61" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L61" t="n">
         <v>0</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -12430,7 +12430,7 @@
         <v>2.4</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -12594,16 +12594,16 @@
         <v>1.41</v>
       </c>
       <c r="G63" t="n">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="H63" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="I63" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="J63" t="n">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="K63" t="n">
         <v>5.1</v>
@@ -12621,10 +12621,10 @@
         <v>0</v>
       </c>
       <c r="P63" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q63" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -12785,19 +12785,19 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G64" t="n">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="H64" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I64" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="J64" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K64" t="n">
         <v>3.9</v>
@@ -12815,10 +12815,10 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -12979,10 +12979,10 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="G65" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="H65" t="n">
         <v>1.52</v>
@@ -12991,10 +12991,10 @@
         <v>1.84</v>
       </c>
       <c r="J65" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K65" t="n">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -13173,16 +13173,16 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="G66" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H66" t="n">
         <v>2.72</v>
       </c>
       <c r="I66" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="J66" t="n">
         <v>2.98</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -13367,19 +13367,19 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G67" t="n">
-        <v>2.72</v>
+        <v>2.92</v>
       </c>
       <c r="H67" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I67" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J67" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K67" t="n">
         <v>3.45</v>
@@ -13400,7 +13400,7 @@
         <v>1.61</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R67" t="n">
         <v>0</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -13594,7 +13594,7 @@
         <v>1.58</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R68" t="n">
         <v>0</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -13755,16 +13755,16 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G69" t="n">
         <v>2.08</v>
       </c>
       <c r="H69" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I69" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J69" t="n">
         <v>3.2</v>
@@ -13788,7 +13788,7 @@
         <v>1.76</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R69" t="n">
         <v>1.29</v>
@@ -13797,7 +13797,7 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U69" t="n">
         <v>2</v>
@@ -13851,7 +13851,7 @@
         <v>25</v>
       </c>
       <c r="AL69" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM69" t="n">
         <v>150</v>
@@ -13872,10 +13872,10 @@
         <v>29</v>
       </c>
       <c r="AS69" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT69" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AU69" t="n">
         <v>6.6</v>
@@ -13908,7 +13908,7 @@
         <v>34</v>
       </c>
       <c r="BE69" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF69" t="n">
         <v>15.5</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -14143,16 +14143,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G71" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H71" t="n">
         <v>5</v>
       </c>
       <c r="I71" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J71" t="n">
         <v>3.4</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -14728,7 +14728,7 @@
         <v>2.26</v>
       </c>
       <c r="G74" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="H74" t="n">
         <v>2.96</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -15307,19 +15307,19 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G77" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="H77" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="I77" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="J77" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="K77" t="n">
         <v>3.45</v>
@@ -15337,10 +15337,10 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -15501,22 +15501,22 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="G78" t="n">
-        <v>2.86</v>
+        <v>2.74</v>
       </c>
       <c r="H78" t="n">
-        <v>2.68</v>
+        <v>2.92</v>
       </c>
       <c r="I78" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="J78" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K78" t="n">
-        <v>6.8</v>
+        <v>4.6</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -15531,10 +15531,10 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -15922,7 +15922,7 @@
         <v>1.24</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -16083,13 +16083,13 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G81" t="n">
         <v>3.6</v>
       </c>
       <c r="H81" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I81" t="n">
         <v>2.22</v>
@@ -16098,7 +16098,7 @@
         <v>3.65</v>
       </c>
       <c r="K81" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -16128,7 +16128,7 @@
         <v>1.73</v>
       </c>
       <c r="U81" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V81" t="n">
         <v>0</v>
@@ -16137,7 +16137,7 @@
         <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y81" t="n">
         <v>11</v>
@@ -16179,10 +16179,10 @@
         <v>40</v>
       </c>
       <c r="AL81" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM81" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN81" t="n">
         <v>36</v>
@@ -16215,13 +16215,13 @@
         <v>19.5</v>
       </c>
       <c r="AX81" t="n">
-        <v>17.5</v>
+        <v>23</v>
       </c>
       <c r="AY81" t="n">
         <v>13.5</v>
       </c>
       <c r="AZ81" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA81" t="n">
         <v>30</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -16510,7 +16510,7 @@
         <v>1.66</v>
       </c>
       <c r="S83" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T83" t="n">
         <v>1.82</v>
@@ -16597,7 +16597,7 @@
         <v>10.5</v>
       </c>
       <c r="AV83" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AW83" t="n">
         <v>38</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -16886,7 +16886,7 @@
         <v>3.8</v>
       </c>
       <c r="O85" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P85" t="n">
         <v>1.93</v>
@@ -16898,10 +16898,10 @@
         <v>1.36</v>
       </c>
       <c r="S85" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T85" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U85" t="n">
         <v>2.16</v>
@@ -16913,7 +16913,7 @@
         <v>0</v>
       </c>
       <c r="X85" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y85" t="n">
         <v>13.5</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -17077,7 +17077,7 @@
         <v>1.09</v>
       </c>
       <c r="N86" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O86" t="n">
         <v>1.41</v>
@@ -17107,7 +17107,7 @@
         <v>0</v>
       </c>
       <c r="X86" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y86" t="n">
         <v>12</v>
@@ -17131,7 +17131,7 @@
         <v>48</v>
       </c>
       <c r="AF86" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG86" t="n">
         <v>11.5</v>
@@ -17206,7 +17206,7 @@
         <v>38</v>
       </c>
       <c r="BE86" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF86" t="n">
         <v>21</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -17280,7 +17280,7 @@
         <v>1.9</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R87" t="n">
         <v>0</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -17441,22 +17441,22 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="G88" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="H88" t="n">
-        <v>1.18</v>
+        <v>6</v>
       </c>
       <c r="I88" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J88" t="n">
-        <v>1.12</v>
+        <v>4</v>
       </c>
       <c r="K88" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -17471,10 +17471,10 @@
         <v>0</v>
       </c>
       <c r="P88" t="n">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -17946,7 +17946,7 @@
         <v>20</v>
       </c>
       <c r="AS90" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT90" t="n">
         <v>7.8</v>
@@ -17982,17 +17982,17 @@
         <v>42</v>
       </c>
       <c r="BE90" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF90" t="n">
         <v>22</v>
       </c>
       <c r="BG90" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="G91" t="n">
         <v>2.92</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -18799,13 +18799,13 @@
         </is>
       </c>
       <c r="F95" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="G95" t="n">
         <v>3.5</v>
       </c>
       <c r="H95" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="I95" t="n">
         <v>3.45</v>
@@ -18829,10 +18829,10 @@
         <v>0</v>
       </c>
       <c r="P95" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="R95" t="n">
         <v>0</v>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -18993,7 +18993,7 @@
         </is>
       </c>
       <c r="F96" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G96" t="n">
         <v>2.74</v>
@@ -19008,7 +19008,7 @@
         <v>3.2</v>
       </c>
       <c r="K96" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="L96" t="n">
         <v>0</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -19199,7 +19199,7 @@
         <v>4.5</v>
       </c>
       <c r="J97" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K97" t="n">
         <v>3.2</v>
@@ -19220,7 +19220,7 @@
         <v>1.45</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -19381,7 +19381,7 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="G98" t="n">
         <v>2.12</v>
@@ -19390,7 +19390,7 @@
         <v>3.65</v>
       </c>
       <c r="I98" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="J98" t="n">
         <v>3.7</v>
@@ -19414,7 +19414,7 @@
         <v>2.16</v>
       </c>
       <c r="Q98" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R98" t="n">
         <v>0</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -19578,16 +19578,16 @@
         <v>1.32</v>
       </c>
       <c r="G99" t="n">
-        <v>6.8</v>
+        <v>2.42</v>
       </c>
       <c r="H99" t="n">
-        <v>1.32</v>
+        <v>3.65</v>
       </c>
       <c r="I99" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="J99" t="n">
-        <v>1.03</v>
+        <v>1.7</v>
       </c>
       <c r="K99" t="n">
         <v>4.1</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -19781,7 +19781,7 @@
         <v>1000</v>
       </c>
       <c r="J100" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K100" t="n">
         <v>950</v>
@@ -19793,7 +19793,7 @@
         <v>1.01</v>
       </c>
       <c r="N100" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O100" t="n">
         <v>1.01</v>
@@ -19802,13 +19802,13 @@
         <v>1.24</v>
       </c>
       <c r="Q100" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="R100" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="S100" t="n">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="T100" t="n">
         <v>1.01</v>
@@ -19877,52 +19877,52 @@
         <v>1000</v>
       </c>
       <c r="AP100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF100" t="n">
         <v>1.01</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -19966,7 +19966,7 @@
         <v>1.87</v>
       </c>
       <c r="G101" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H101" t="n">
         <v>3.4</v>
@@ -19993,10 +19993,10 @@
         <v>0</v>
       </c>
       <c r="P101" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="Q101" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R101" t="n">
         <v>0</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -20187,10 +20187,10 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>1.24</v>
+        <v>1.57</v>
       </c>
       <c r="Q102" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R102" t="n">
         <v>0</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -20360,10 +20360,10 @@
         <v>4.7</v>
       </c>
       <c r="I103" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="J103" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K103" t="n">
         <v>4.2</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -20739,22 +20739,22 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="G105" t="n">
         <v>2.12</v>
       </c>
       <c r="H105" t="n">
-        <v>3.75</v>
+        <v>1.93</v>
       </c>
       <c r="I105" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J105" t="n">
         <v>3.4</v>
       </c>
       <c r="K105" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="L105" t="n">
         <v>0</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -21130,7 +21130,7 @@
         <v>2.66</v>
       </c>
       <c r="G107" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H107" t="n">
         <v>2.62</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -21515,16 +21515,16 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G109" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H109" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="I109" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="J109" t="n">
         <v>3.45</v>
@@ -21545,10 +21545,10 @@
         <v>0</v>
       </c>
       <c r="P109" t="n">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="Q109" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R109" t="n">
         <v>0</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -21721,7 +21721,7 @@
         <v>11.5</v>
       </c>
       <c r="J110" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="K110" t="n">
         <v>5.7</v>
@@ -21748,7 +21748,7 @@
         <v>1.5</v>
       </c>
       <c r="S110" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T110" t="n">
         <v>2.16</v>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -21930,19 +21930,19 @@
         <v>6.8</v>
       </c>
       <c r="O111" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P111" t="n">
         <v>2.74</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R111" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="S111" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="T111" t="n">
         <v>1.68</v>
@@ -22011,7 +22011,7 @@
         <v>4.2</v>
       </c>
       <c r="AP111" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ111" t="n">
         <v>12</v>
@@ -22023,7 +22023,7 @@
         <v>12</v>
       </c>
       <c r="AT111" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU111" t="n">
         <v>12.5</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -22100,7 +22100,7 @@
         <v>2.36</v>
       </c>
       <c r="G112" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="H112" t="n">
         <v>3.55</v>
@@ -22124,13 +22124,13 @@
         <v>2.96</v>
       </c>
       <c r="O112" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="P112" t="n">
         <v>1.64</v>
       </c>
       <c r="Q112" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R112" t="n">
         <v>1.23</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -22291,7 +22291,7 @@
         </is>
       </c>
       <c r="F113" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G113" t="n">
         <v>1.76</v>
@@ -22300,7 +22300,7 @@
         <v>5.7</v>
       </c>
       <c r="I113" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J113" t="n">
         <v>3.8</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -22530,7 +22530,7 @@
         <v>1.73</v>
       </c>
       <c r="U114" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V114" t="n">
         <v>0</v>
@@ -22545,7 +22545,7 @@
         <v>12.5</v>
       </c>
       <c r="Z114" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA114" t="n">
         <v>50</v>
@@ -22560,7 +22560,7 @@
         <v>13</v>
       </c>
       <c r="AE114" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF114" t="n">
         <v>17.5</v>
@@ -22572,7 +22572,7 @@
         <v>16.5</v>
       </c>
       <c r="AI114" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="AJ114" t="n">
         <v>38</v>
@@ -22581,7 +22581,7 @@
         <v>27</v>
       </c>
       <c r="AL114" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM114" t="n">
         <v>80</v>
@@ -22593,7 +22593,7 @@
         <v>28</v>
       </c>
       <c r="AP114" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AQ114" t="n">
         <v>11.5</v>
@@ -22602,7 +22602,7 @@
         <v>18.5</v>
       </c>
       <c r="AS114" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AT114" t="n">
         <v>10.5</v>
@@ -22614,10 +22614,10 @@
         <v>11.5</v>
       </c>
       <c r="AW114" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AX114" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY114" t="n">
         <v>11</v>
@@ -22626,29 +22626,29 @@
         <v>15.5</v>
       </c>
       <c r="BA114" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB114" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BC114" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD114" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BE114" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BF114" t="n">
         <v>19</v>
       </c>
       <c r="BG114" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -22691,7 +22691,7 @@
         <v>1000</v>
       </c>
       <c r="J115" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K115" t="n">
         <v>950</v>
@@ -22712,13 +22712,13 @@
         <v>1.24</v>
       </c>
       <c r="Q115" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="R115" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="S115" t="n">
-        <v>1.02</v>
+        <v>1.51</v>
       </c>
       <c r="T115" t="n">
         <v>1.01</v>
@@ -22787,52 +22787,52 @@
         <v>1000</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE115" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF115" t="n">
         <v>1.01</v>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -22876,7 +22876,7 @@
         <v>2.3</v>
       </c>
       <c r="G116" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H116" t="n">
         <v>3.25</v>
@@ -22885,7 +22885,7 @@
         <v>3.3</v>
       </c>
       <c r="J116" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K116" t="n">
         <v>3.9</v>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -23270,10 +23270,10 @@
         <v>2.78</v>
       </c>
       <c r="I118" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="J118" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K118" t="n">
         <v>3.2</v>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -23467,10 +23467,10 @@
         <v>3.75</v>
       </c>
       <c r="J119" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K119" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L119" t="n">
         <v>0</v>
@@ -23485,7 +23485,7 @@
         <v>0</v>
       </c>
       <c r="P119" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="Q119" t="n">
         <v>3</v>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -23661,7 +23661,7 @@
         <v>1000</v>
       </c>
       <c r="J120" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K120" t="n">
         <v>950</v>
@@ -23682,13 +23682,13 @@
         <v>1.24</v>
       </c>
       <c r="Q120" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="R120" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="S120" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="T120" t="n">
         <v>1.01</v>
@@ -23757,52 +23757,52 @@
         <v>1000</v>
       </c>
       <c r="AP120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE120" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF120" t="n">
         <v>1.01</v>
@@ -23812,7 +23812,7 @@
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -23843,16 +23843,16 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="G121" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H121" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="I121" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J121" t="n">
         <v>3.55</v>
@@ -24006,7 +24006,7 @@
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -24200,7 +24200,7 @@
       </c>
       <c r="BH122" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -24394,7 +24394,7 @@
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -24437,7 +24437,7 @@
         <v>1000</v>
       </c>
       <c r="J124" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K124" t="n">
         <v>950</v>
@@ -24449,7 +24449,7 @@
         <v>1.01</v>
       </c>
       <c r="N124" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O124" t="n">
         <v>1.01</v>
@@ -24458,13 +24458,13 @@
         <v>1.24</v>
       </c>
       <c r="Q124" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="R124" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="S124" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="T124" t="n">
         <v>1.01</v>
@@ -24533,52 +24533,52 @@
         <v>1000</v>
       </c>
       <c r="AP124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE124" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF124" t="n">
         <v>1.01</v>
@@ -24588,7 +24588,7 @@
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -24619,22 +24619,22 @@
         </is>
       </c>
       <c r="F125" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="G125" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="H125" t="n">
-        <v>2.86</v>
+        <v>12.5</v>
       </c>
       <c r="I125" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="J125" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K125" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L125" t="n">
         <v>0</v>
@@ -24649,10 +24649,10 @@
         <v>0</v>
       </c>
       <c r="P125" t="n">
-        <v>1.54</v>
+        <v>1.63</v>
       </c>
       <c r="Q125" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="R125" t="n">
         <v>0</v>
@@ -24782,7 +24782,7 @@
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -24816,7 +24816,7 @@
         <v>2</v>
       </c>
       <c r="G126" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H126" t="n">
         <v>4.6</v>
@@ -24843,7 +24843,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q126" t="n">
         <v>2.68</v>
@@ -24976,7 +24976,7 @@
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -25013,7 +25013,7 @@
         <v>2.14</v>
       </c>
       <c r="H127" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="I127" t="n">
         <v>4.7</v>
@@ -25170,7 +25170,7 @@
       </c>
       <c r="BH127" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -25201,10 +25201,10 @@
         </is>
       </c>
       <c r="F128" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="G128" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H128" t="n">
         <v>3.4</v>
@@ -25213,10 +25213,10 @@
         <v>4.3</v>
       </c>
       <c r="J128" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K128" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -25364,7 +25364,7 @@
       </c>
       <c r="BH128" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
@@ -25558,7 +25558,7 @@
       </c>
       <c r="BH129" t="inlineStr">
         <is>
-          <t>2026-03-19 01:43:43</t>
+          <t>2026-03-19 04:01:01</t>
         </is>
       </c>
     </row>
